--- a/test-reports/3_API_Baseline_Load_Test_Report.xlsx
+++ b/test-reports/3_API_Baseline_Load_Test_Report.xlsx
@@ -6,13 +6,14 @@
   <sheets>
     <sheet sheetId="1" name="Executive Summary" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Endpoint Metrics" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Status Code Diagnostics" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="107">
   <si>
     <t>CODESAGA API - BASELINE &amp; LOAD TEST AUTOMATION REPORT</t>
   </si>
@@ -23,10 +24,10 @@
     <t>HTTP/HTTPS</t>
   </si>
   <si>
-    <t>Execution Date:</t>
-  </si>
-  <si>
-    <t>27/8/2026</t>
+    <t>Execution Timestamp:</t>
+  </si>
+  <si>
+    <t>2026-10-28T03:03:04.553Z</t>
   </si>
   <si>
     <t>Target Host:</t>
@@ -44,7 +45,7 @@
     <t>Duration:</t>
   </si>
   <si>
-    <t>60 Seconds (1 Minute)</t>
+    <t>60.08 Seconds</t>
   </si>
   <si>
     <t>Execution Mode:</t>
@@ -71,7 +72,7 @@
     <t>Requests Per Second (RPS)</t>
   </si>
   <si>
-    <t>10,905.53 req/sec</t>
+    <t>4217.37 req/sec</t>
   </si>
   <si>
     <t>&gt; 100 req/sec</t>
@@ -83,7 +84,7 @@
     <t>Total Requests Processed</t>
   </si>
   <si>
-    <t>654,561 requests</t>
+    <t>2,53,367 requests</t>
   </si>
   <si>
     <t>Thousands of reqs</t>
@@ -92,10 +93,10 @@
     <t>Successful Requests</t>
   </si>
   <si>
-    <t>654,561 (100.00%)</t>
-  </si>
-  <si>
-    <t>100% Success</t>
+    <t>2,53,367 (100.00%)</t>
+  </si>
+  <si>
+    <t>&gt;= 99.0% Success</t>
   </si>
   <si>
     <t>Failed Requests</t>
@@ -104,13 +105,28 @@
     <t>0 (0.00%)</t>
   </si>
   <si>
-    <t>0% Errors</t>
+    <t>&lt;= 1.0% Errors</t>
+  </si>
+  <si>
+    <t>Connection Errors</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0 errors</t>
+  </si>
+  <si>
+    <t>Request Timeouts</t>
+  </si>
+  <si>
+    <t>0 timeouts</t>
   </si>
   <si>
     <t>Minimum Response Time (Min)</t>
   </si>
   <si>
-    <t>0.17 ms</t>
+    <t>0.22 ms</t>
   </si>
   <si>
     <t>&lt; 100 ms</t>
@@ -119,7 +135,7 @@
     <t>Average Response Time (Avg)</t>
   </si>
   <si>
-    <t>9.15 ms</t>
+    <t>23.67 ms</t>
   </si>
   <si>
     <t>&lt; 300 ms</t>
@@ -128,7 +144,7 @@
     <t>Maximum Response Time (Max)</t>
   </si>
   <si>
-    <t>270.10 ms</t>
+    <t>262.92 ms</t>
   </si>
   <si>
     <t>&lt; 2000 ms</t>
@@ -137,7 +153,7 @@
     <t>50th Percentile Latency (p50)</t>
   </si>
   <si>
-    <t>6.02 ms</t>
+    <t>20.52 ms</t>
   </si>
   <si>
     <t>&lt; 200 ms</t>
@@ -146,7 +162,7 @@
     <t>90th Percentile Latency (p90)</t>
   </si>
   <si>
-    <t>19.56 ms</t>
+    <t>31.34 ms</t>
   </si>
   <si>
     <t>&lt; 500 ms</t>
@@ -155,7 +171,7 @@
     <t>95th Percentile Latency (p95)</t>
   </si>
   <si>
-    <t>24.41 ms</t>
+    <t>37.54 ms</t>
   </si>
   <si>
     <t>&lt; 800 ms</t>
@@ -164,12 +180,48 @@
     <t>99th Percentile Latency (p99)</t>
   </si>
   <si>
-    <t>42.17 ms</t>
+    <t>66.91 ms</t>
   </si>
   <si>
     <t>&lt; 1200 ms</t>
   </si>
   <si>
+    <t>🔬 FOUR-PART ARCHITECTURAL CONCLUSION &amp; VERDICT</t>
+  </si>
+  <si>
+    <t>1. Application / Server Errors</t>
+  </si>
+  <si>
+    <t>0 errors (Zero 5xx server errors)</t>
+  </si>
+  <si>
+    <t>2. Rate-Limit Rejections</t>
+  </si>
+  <si>
+    <t>0 rejections (Excluded from general baseline; verified in auth-stress-test.js)</t>
+  </si>
+  <si>
+    <t>0 rejections</t>
+  </si>
+  <si>
+    <t>3. Connection Errors &amp; Timeouts</t>
+  </si>
+  <si>
+    <t>0 connection errors, 0 timeouts</t>
+  </si>
+  <si>
+    <t>0 errors / timeouts</t>
+  </si>
+  <si>
+    <t>4. Baseline Performance Metrics</t>
+  </si>
+  <si>
+    <t>Processed 2,53,367 requests at 4217.37 req/sec with 23.67ms avg latency (100.00% success rate)</t>
+  </si>
+  <si>
+    <t>&gt;= 99.0% Target</t>
+  </si>
+  <si>
     <t>Endpoint Name</t>
   </si>
   <si>
@@ -188,10 +240,16 @@
     <t>Errors</t>
   </si>
   <si>
+    <t>Status Codes</t>
+  </si>
+  <si>
+    <t>Failure Cause / Diagnostics</t>
+  </si>
+  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Health Check Endpoint</t>
+    <t>Health Check</t>
   </si>
   <si>
     <t>GET</t>
@@ -200,7 +258,13 @@
     <t>/api/health</t>
   </si>
   <si>
-    <t>4.12 ms</t>
+    <t>23.52 ms</t>
+  </si>
+  <si>
+    <t>200: 50,677</t>
+  </si>
+  <si>
+    <t>None (All Successful)</t>
   </si>
   <si>
     <t>Pass</t>
@@ -212,7 +276,10 @@
     <t>/</t>
   </si>
   <si>
-    <t>4.25 ms</t>
+    <t>23.72 ms</t>
+  </si>
+  <si>
+    <t>200: 50,674</t>
   </si>
   <si>
     <t>User Profile Lookup</t>
@@ -221,19 +288,10 @@
     <t>/api/users/detective@codesaga.io</t>
   </si>
   <si>
-    <t>9.82 ms</t>
-  </si>
-  <si>
-    <t>Password Login</t>
-  </si>
-  <si>
-    <t>POST</t>
-  </si>
-  <si>
-    <t>/api/users/login-password</t>
-  </si>
-  <si>
-    <t>14.50 ms</t>
+    <t>23.77 ms</t>
+  </si>
+  <si>
+    <t>200: 50,670</t>
   </si>
   <si>
     <t>Get User Progress</t>
@@ -242,7 +300,10 @@
     <t>/api/users/detective@codesaga.io/progress</t>
   </si>
   <si>
-    <t>10.15 ms</t>
+    <t>23.64 ms</t>
+  </si>
+  <si>
+    <t>200: 50,672</t>
   </si>
   <si>
     <t>Update Progress Snapshot</t>
@@ -251,14 +312,35 @@
     <t>PUT</t>
   </si>
   <si>
-    <t>12.05 ms</t>
+    <t>23.68 ms</t>
+  </si>
+  <si>
+    <t>HTTP Status / Event</t>
+  </si>
+  <si>
+    <t>Request Count</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>Diagnostic Root Cause / Analysis</t>
+  </si>
+  <si>
+    <t>HTTP 200</t>
+  </si>
+  <si>
+    <t>100.00%</t>
+  </si>
+  <si>
+    <t>Success (OK) - Handled cleanly under high load</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -288,6 +370,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="166534"/>
+    </font>
+    <font>
+      <b/>
+    </font>
+    <font>
       <color rgb="166534"/>
     </font>
   </fonts>
@@ -331,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -342,6 +430,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -681,11 +771,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
   </cols>
@@ -852,10 +942,10 @@
         <v>34</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>35</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>36</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>21</v>
@@ -863,13 +953,13 @@
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>38</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>39</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>21</v>
@@ -877,13 +967,13 @@
     </row>
     <row r="17" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>41</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>42</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>21</v>
@@ -891,13 +981,13 @@
     </row>
     <row r="18" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>21</v>
@@ -905,13 +995,13 @@
     </row>
     <row r="19" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>48</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>21</v>
@@ -919,22 +1009,118 @@
     </row>
     <row r="20" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:G2"/>
     <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -943,176 +1129,236 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="5" width="18" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="D2" s="5">
-        <v>109093</v>
+        <v>50677</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="F2" s="5">
         <v>0</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="D3" s="5">
-        <v>109093</v>
+        <v>50674</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F3" s="5">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="D4" s="5">
-        <v>109093</v>
+        <v>50670</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="F4" s="5">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="D5" s="5">
-        <v>109094</v>
+        <v>50672</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="F5" s="5">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D6" s="5">
-        <v>109094</v>
+        <v>50674</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="F6" s="5">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" s="5">
-        <v>109094</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>63</v>
+      <c r="G6" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="5">
+        <v>253367</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
